--- a/Tipos de trabajo/output/subclasificacion_instalaciones.xlsx
+++ b/Tipos de trabajo/output/subclasificacion_instalaciones.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dacm/we/odoo_con_trabajos/Tipos de trabajo/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00EFA3CC-ECA7-7D48-A7B3-C625E2926419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F2E65A-465C-6F43-A877-47310FF8F5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33600" yWindow="-5560" windowWidth="38400" windowHeight="19920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-5560" windowWidth="33720" windowHeight="19920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reasignación" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,11 @@
     <sheet name="Definiciones" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Reasignación!$A$1:$R$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Reasignación!$A$1:$R$113</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="176" r:id="rId4"/>
+    <pivotCache cacheId="277" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1815,7 +1815,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1840,14 +1840,11 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5250,7 +5247,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6EA3F32-27E8-854C-B655-88C820D27214}" name="TablaDinámica10" cacheId="176" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B6EA3F32-27E8-854C-B655-88C820D27214}" name="TablaDinámica10" cacheId="277" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField dataField="1" showAll="0"/>
@@ -5346,7 +5343,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B899D2A-9BDC-F84E-90B3-95536422A40E}" name="TablaDinámica1" cacheId="176" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B899D2A-9BDC-F84E-90B3-95536422A40E}" name="TablaDinámica1" cacheId="277" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="E3:F40" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField dataField="1" showAll="0"/>
@@ -5845,6 +5842,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R113"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -5915,7 +5913,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>76</v>
       </c>
@@ -5968,7 +5966,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>82</v>
       </c>
@@ -6021,57 +6019,56 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="14">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A4">
         <v>84</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" t="s">
         <v>356</v>
       </c>
-      <c r="D4" s="14" t="s">
+      <c r="D4" t="s">
         <v>429</v>
       </c>
-      <c r="E4" s="14" t="s">
+      <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" t="s">
         <v>362</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="5">
         <v>45896</v>
       </c>
-      <c r="I4" s="14" t="s">
+      <c r="I4" t="s">
         <v>142</v>
       </c>
-      <c r="J4" s="14" t="s">
+      <c r="J4" t="s">
         <v>363</v>
       </c>
-      <c r="K4" s="14">
+      <c r="K4">
         <v>3</v>
       </c>
-      <c r="L4" s="14" t="s">
+      <c r="L4" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="14" t="s">
+      <c r="M4" t="s">
         <v>25</v>
       </c>
-      <c r="N4" s="14" t="s">
+      <c r="N4" t="s">
         <v>172</v>
       </c>
-      <c r="O4" s="14" t="s">
+      <c r="O4" t="s">
         <v>364</v>
       </c>
-      <c r="P4" s="14" t="s">
+      <c r="P4" t="s">
         <v>28</v>
       </c>
-      <c r="Q4" s="14"/>
-      <c r="R4" s="14" t="s">
+      <c r="R4" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6172,7 +6169,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>84</v>
       </c>
@@ -6225,7 +6222,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>90</v>
       </c>
@@ -6272,215 +6269,207 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="14">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A9">
         <v>96</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" t="s">
         <v>328</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" t="s">
         <v>429</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H9" s="5">
         <v>45902</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" t="s">
         <v>219</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" t="s">
         <v>329</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9">
         <v>3</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" t="s">
         <v>25</v>
       </c>
-      <c r="N9" s="14" t="s">
+      <c r="N9" t="s">
         <v>61</v>
       </c>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14" t="s">
+      <c r="P9" t="s">
         <v>28</v>
       </c>
-      <c r="Q9" s="14"/>
-      <c r="R9" s="14" t="s">
+      <c r="R9" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A10">
         <v>96</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" t="s">
         <v>328</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" t="s">
         <v>429</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" t="s">
         <v>80</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H10" s="5">
         <v>45902</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" t="s">
         <v>219</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" t="s">
         <v>329</v>
       </c>
-      <c r="K10" s="14">
+      <c r="K10">
         <v>3</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="L10" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="14" t="s">
+      <c r="M10" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="14" t="s">
+      <c r="N10" t="s">
         <v>61</v>
       </c>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14" t="s">
+      <c r="P10" t="s">
         <v>28</v>
       </c>
-      <c r="Q10" s="14"/>
-      <c r="R10" s="14" t="s">
+      <c r="R10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="14">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A11">
         <v>95</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" t="s">
         <v>330</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" t="s">
         <v>429</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H11" s="5">
         <v>45902</v>
       </c>
-      <c r="I11" s="14" t="s">
+      <c r="I11" t="s">
         <v>219</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" t="s">
         <v>331</v>
       </c>
-      <c r="K11" s="14">
+      <c r="K11">
         <v>3</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="L11" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="14" t="s">
+      <c r="M11" t="s">
         <v>42</v>
       </c>
-      <c r="N11" s="14" t="s">
+      <c r="N11" t="s">
         <v>242</v>
       </c>
-      <c r="O11" s="14"/>
-      <c r="P11" s="14" t="s">
+      <c r="P11" t="s">
         <v>28</v>
       </c>
-      <c r="Q11" s="14"/>
-      <c r="R11" s="14" t="s">
+      <c r="R11" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="14">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A12">
         <v>95</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" t="s">
         <v>330</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" t="s">
         <v>429</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="5">
         <v>45902</v>
       </c>
-      <c r="I12" s="14" t="s">
+      <c r="I12" t="s">
         <v>219</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" t="s">
         <v>331</v>
       </c>
-      <c r="K12" s="14">
+      <c r="K12">
         <v>3</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="14" t="s">
+      <c r="M12" t="s">
         <v>25</v>
       </c>
-      <c r="N12" s="14" t="s">
+      <c r="N12" t="s">
         <v>61</v>
       </c>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14" t="s">
+      <c r="P12" t="s">
         <v>28</v>
       </c>
-      <c r="Q12" s="14"/>
-      <c r="R12" s="14" t="s">
+      <c r="R12" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>93</v>
       </c>
@@ -6533,7 +6522,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>93</v>
       </c>
@@ -6586,7 +6575,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>101</v>
       </c>
@@ -6639,7 +6628,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>99</v>
       </c>
@@ -6687,54 +6676,52 @@
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="14">
+      <c r="A17">
         <v>104</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" t="s">
         <v>312</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" t="s">
         <v>429</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="E17" t="s">
         <v>19</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" t="s">
         <v>313</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="15">
+      <c r="H17" s="5">
         <v>45904</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" t="s">
         <v>142</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" t="s">
         <v>314</v>
       </c>
-      <c r="K17" s="14">
+      <c r="K17">
         <v>3</v>
       </c>
-      <c r="L17" s="14" t="s">
+      <c r="L17" t="s">
         <v>24</v>
       </c>
-      <c r="M17" s="14" t="s">
+      <c r="M17" t="s">
         <v>25</v>
       </c>
-      <c r="N17" s="14" t="s">
+      <c r="N17" t="s">
         <v>315</v>
       </c>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14" t="s">
+      <c r="P17" t="s">
         <v>28</v>
       </c>
-      <c r="Q17" s="14"/>
-      <c r="R17" s="14" t="s">
+      <c r="R17" t="s">
         <v>39</v>
       </c>
     </row>
@@ -6786,110 +6773,106 @@
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="14">
+      <c r="A19">
         <v>108</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" t="s">
         <v>297</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" t="s">
         <v>429</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="E19" t="s">
         <v>19</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" t="s">
         <v>298</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" t="s">
         <v>21</v>
       </c>
-      <c r="H19" s="15">
+      <c r="H19" s="5">
         <v>45905</v>
       </c>
-      <c r="I19" s="14" t="s">
+      <c r="I19" t="s">
         <v>142</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" t="s">
         <v>299</v>
       </c>
-      <c r="K19" s="14">
+      <c r="K19">
         <v>3</v>
       </c>
-      <c r="L19" s="14" t="s">
+      <c r="L19" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="14" t="s">
+      <c r="M19" t="s">
         <v>25</v>
       </c>
-      <c r="N19" s="14" t="s">
+      <c r="N19" t="s">
         <v>300</v>
       </c>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14" t="s">
+      <c r="P19" t="s">
         <v>28</v>
       </c>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14" t="s">
+      <c r="R19" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="14">
+      <c r="A20">
         <v>108</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" t="s">
         <v>297</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" t="s">
         <v>429</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" t="s">
         <v>19</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" t="s">
         <v>293</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" t="s">
         <v>21</v>
       </c>
-      <c r="H20" s="15">
+      <c r="H20" s="5">
         <v>45905</v>
       </c>
-      <c r="I20" s="14" t="s">
+      <c r="I20" t="s">
         <v>142</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" t="s">
         <v>301</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20">
         <v>3</v>
       </c>
-      <c r="L20" s="14" t="s">
+      <c r="L20" t="s">
         <v>24</v>
       </c>
-      <c r="M20" s="14" t="s">
+      <c r="M20" t="s">
         <v>25</v>
       </c>
-      <c r="N20" s="14" t="s">
+      <c r="N20" t="s">
         <v>295</v>
       </c>
-      <c r="O20" s="14"/>
-      <c r="P20" s="14" t="s">
+      <c r="P20" t="s">
         <v>28</v>
       </c>
-      <c r="Q20" s="14"/>
-      <c r="R20" s="14" t="s">
+      <c r="R20" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>105</v>
       </c>
@@ -6939,99 +6922,91 @@
         <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A22" s="14">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A22">
         <v>105</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" t="s">
         <v>307</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" t="s">
         <v>427</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" t="s">
         <v>132</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" t="s">
         <v>308</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" t="s">
         <v>381</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="5">
         <v>45905</v>
       </c>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14" t="s">
+      <c r="J22" t="s">
         <v>310</v>
       </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14" t="s">
+      <c r="P22" t="s">
         <v>384</v>
       </c>
-      <c r="Q22" s="14" t="s">
+      <c r="Q22" t="s">
         <v>21</v>
       </c>
-      <c r="R22" s="14" t="s">
+      <c r="R22" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A23" s="14">
+      <c r="A23">
         <v>116</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" t="s">
         <v>292</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" t="s">
         <v>429</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" t="s">
         <v>19</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" t="s">
         <v>293</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" t="s">
         <v>21</v>
       </c>
-      <c r="H23" s="15">
+      <c r="H23" s="5">
         <v>45909</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" t="s">
         <v>142</v>
       </c>
-      <c r="J23" s="14" t="s">
+      <c r="J23" t="s">
         <v>294</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23">
         <v>3</v>
       </c>
-      <c r="L23" s="14" t="s">
+      <c r="L23" t="s">
         <v>24</v>
       </c>
-      <c r="M23" s="14" t="s">
+      <c r="M23" t="s">
         <v>25</v>
       </c>
-      <c r="N23" s="14" t="s">
+      <c r="N23" t="s">
         <v>295</v>
       </c>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14" t="s">
+      <c r="P23" t="s">
         <v>28</v>
       </c>
-      <c r="Q23" s="14"/>
-      <c r="R23" s="14" t="s">
+      <c r="R23" t="s">
         <v>39</v>
       </c>
     </row>
@@ -7085,7 +7060,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>118</v>
       </c>
@@ -7344,7 +7319,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>117</v>
       </c>
@@ -7397,7 +7372,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>117</v>
       </c>
@@ -7451,110 +7426,108 @@
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A32" s="14">
+      <c r="A32">
         <v>122</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" t="s">
         <v>257</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" t="s">
         <v>429</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E32" t="s">
         <v>19</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F32" t="s">
         <v>260</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" t="s">
         <v>21</v>
       </c>
-      <c r="H32" s="15">
+      <c r="H32" s="5">
         <v>45911</v>
       </c>
-      <c r="I32" s="14" t="s">
+      <c r="I32" t="s">
         <v>219</v>
       </c>
-      <c r="J32" s="14" t="s">
+      <c r="J32" t="s">
         <v>261</v>
       </c>
-      <c r="K32" s="14">
+      <c r="K32">
         <v>3</v>
       </c>
-      <c r="L32" s="14" t="s">
+      <c r="L32" t="s">
         <v>24</v>
       </c>
-      <c r="M32" s="14" t="s">
+      <c r="M32" t="s">
         <v>25</v>
       </c>
-      <c r="N32" s="14" t="s">
+      <c r="N32" t="s">
         <v>262</v>
       </c>
-      <c r="O32" s="14" t="s">
+      <c r="O32" t="s">
         <v>38</v>
       </c>
-      <c r="P32" s="14" t="s">
+      <c r="P32" t="s">
         <v>28</v>
       </c>
-      <c r="Q32" s="14"/>
-      <c r="R32" s="14" t="s">
+      <c r="R32" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A33" s="14">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A33">
         <v>124</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B33" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" t="s">
         <v>251</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" t="s">
         <v>429</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="E33" t="s">
         <v>19</v>
       </c>
-      <c r="F33" s="14" t="s">
+      <c r="F33" t="s">
         <v>49</v>
       </c>
-      <c r="G33" s="14" t="s">
+      <c r="G33" t="s">
         <v>21</v>
       </c>
-      <c r="H33" s="15">
+      <c r="H33" s="5">
         <v>45911</v>
       </c>
-      <c r="I33" s="14" t="s">
+      <c r="I33" t="s">
         <v>81</v>
       </c>
-      <c r="J33" s="14" t="s">
+      <c r="J33" t="s">
         <v>252</v>
       </c>
-      <c r="K33" s="14">
+      <c r="K33">
         <v>3</v>
       </c>
-      <c r="L33" s="14" t="s">
+      <c r="L33" t="s">
         <v>35</v>
       </c>
-      <c r="M33" s="14" t="s">
+      <c r="M33" t="s">
         <v>253</v>
       </c>
-      <c r="N33" s="14" t="s">
+      <c r="N33" t="s">
         <v>254</v>
       </c>
-      <c r="O33" s="14" t="s">
+      <c r="O33" t="s">
         <v>254</v>
       </c>
-      <c r="P33" s="14" t="s">
+      <c r="P33" t="s">
         <v>28</v>
       </c>
-      <c r="Q33" s="14"/>
-      <c r="R33" s="14" t="s">
+      <c r="R33" t="s">
         <v>39</v>
       </c>
     </row>
@@ -7917,113 +7890,110 @@
         <v>39</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A41" s="14">
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A41">
         <v>133</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B41" t="s">
         <v>17</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" t="s">
         <v>240</v>
       </c>
-      <c r="D41" s="14" t="s">
+      <c r="D41" t="s">
         <v>429</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" t="s">
         <v>19</v>
       </c>
-      <c r="F41" s="14" t="s">
+      <c r="F41" t="s">
         <v>63</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" t="s">
         <v>21</v>
       </c>
-      <c r="H41" s="15">
+      <c r="H41" s="5">
         <v>45916</v>
       </c>
-      <c r="I41" s="14" t="s">
+      <c r="I41" t="s">
         <v>219</v>
       </c>
-      <c r="J41" s="14" t="s">
+      <c r="J41" t="s">
         <v>241</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41">
         <v>3</v>
       </c>
-      <c r="L41" s="14" t="s">
+      <c r="L41" t="s">
         <v>24</v>
       </c>
-      <c r="M41" s="14" t="s">
+      <c r="M41" t="s">
         <v>25</v>
       </c>
-      <c r="N41" s="14" t="s">
+      <c r="N41" t="s">
         <v>242</v>
       </c>
-      <c r="O41" s="14"/>
-      <c r="P41" s="14" t="s">
+      <c r="P41" t="s">
         <v>28</v>
       </c>
-      <c r="Q41" s="14"/>
-      <c r="R41" s="14" t="s">
+      <c r="R41" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A42" s="14">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A42">
         <v>136</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" t="s">
         <v>30</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" t="s">
         <v>236</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="D42" t="s">
         <v>429</v>
       </c>
-      <c r="E42" s="14" t="s">
+      <c r="E42" t="s">
         <v>19</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" t="s">
         <v>63</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" t="s">
         <v>21</v>
       </c>
-      <c r="H42" s="15">
+      <c r="H42" s="5">
         <v>45917</v>
       </c>
-      <c r="I42" s="14" t="s">
+      <c r="I42" t="s">
         <v>142</v>
       </c>
-      <c r="J42" s="14" t="s">
+      <c r="J42" t="s">
         <v>237</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42">
         <v>3</v>
       </c>
-      <c r="L42" s="14" t="s">
+      <c r="L42" t="s">
         <v>24</v>
       </c>
-      <c r="M42" s="14" t="s">
+      <c r="M42" t="s">
         <v>25</v>
       </c>
-      <c r="N42" s="14" t="s">
+      <c r="N42" t="s">
         <v>238</v>
       </c>
-      <c r="O42" s="14" t="s">
+      <c r="O42" t="s">
         <v>239</v>
       </c>
-      <c r="P42" s="14" t="s">
+      <c r="P42" t="s">
         <v>28</v>
       </c>
-      <c r="Q42" s="14"/>
-      <c r="R42" s="14" t="s">
+      <c r="R42" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>139</v>
       </c>
@@ -8120,181 +8090,158 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A45" s="14">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A45">
         <v>148</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B45" t="s">
         <v>145</v>
       </c>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14" t="s">
+      <c r="D45" t="s">
         <v>427</v>
       </c>
-      <c r="E45" s="14" t="s">
+      <c r="E45" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="14" t="s">
+      <c r="F45" t="s">
         <v>432</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" t="s">
         <v>381</v>
       </c>
-      <c r="H45" s="15">
+      <c r="H45" s="5">
         <v>45924</v>
       </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14" t="s">
+      <c r="J45" t="s">
         <v>435</v>
       </c>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="14" t="s">
+      <c r="P45" t="s">
         <v>384</v>
       </c>
-      <c r="Q45" s="14" t="s">
+      <c r="Q45" t="s">
         <v>21</v>
       </c>
-      <c r="R45" s="14" t="s">
+      <c r="R45" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A46" s="14">
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A46">
         <v>148</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" t="s">
         <v>145</v>
       </c>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14" t="s">
+      <c r="D46" t="s">
         <v>427</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="E46" t="s">
         <v>132</v>
       </c>
-      <c r="F46" s="14" t="s">
+      <c r="F46" t="s">
         <v>433</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" t="s">
         <v>381</v>
       </c>
-      <c r="H46" s="15">
+      <c r="H46" s="5">
         <v>45924</v>
       </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14" t="s">
+      <c r="J46" t="s">
         <v>435</v>
       </c>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="14" t="s">
+      <c r="P46" t="s">
         <v>384</v>
       </c>
-      <c r="Q46" s="14" t="s">
+      <c r="Q46" t="s">
         <v>21</v>
       </c>
-      <c r="R46" s="14" t="s">
+      <c r="R46" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A47" s="14">
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A47">
         <v>148</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B47" t="s">
         <v>145</v>
       </c>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14" t="s">
+      <c r="D47" t="s">
         <v>427</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="E47" t="s">
         <v>132</v>
       </c>
-      <c r="F47" s="14" t="s">
+      <c r="F47" t="s">
         <v>434</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" t="s">
         <v>381</v>
       </c>
-      <c r="H47" s="15">
+      <c r="H47" s="5">
         <v>45924</v>
       </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14" t="s">
+      <c r="J47" t="s">
         <v>435</v>
       </c>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="14" t="s">
+      <c r="P47" t="s">
         <v>384</v>
       </c>
-      <c r="Q47" s="14" t="s">
+      <c r="Q47" t="s">
         <v>21</v>
       </c>
-      <c r="R47" s="14" t="s">
+      <c r="R47" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A48" s="14">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A48">
         <v>154</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B48" t="s">
         <v>30</v>
       </c>
-      <c r="C48" s="14" t="s">
+      <c r="C48" t="s">
         <v>221</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="D48" t="s">
         <v>429</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="E48" t="s">
         <v>19</v>
       </c>
-      <c r="F48" s="14" t="s">
+      <c r="F48" t="s">
         <v>177</v>
       </c>
-      <c r="G48" s="14" t="s">
+      <c r="G48" t="s">
         <v>21</v>
       </c>
-      <c r="H48" s="15">
+      <c r="H48" s="5">
         <v>45925</v>
       </c>
-      <c r="I48" s="14" t="s">
+      <c r="I48" t="s">
         <v>142</v>
       </c>
-      <c r="J48" s="14" t="s">
+      <c r="J48" t="s">
         <v>222</v>
       </c>
-      <c r="K48" s="14">
+      <c r="K48">
         <v>3</v>
       </c>
-      <c r="L48" s="14" t="s">
+      <c r="L48" t="s">
         <v>24</v>
       </c>
-      <c r="M48" s="14" t="s">
+      <c r="M48" t="s">
         <v>25</v>
       </c>
-      <c r="N48" s="14" t="s">
+      <c r="N48" t="s">
         <v>223</v>
       </c>
-      <c r="O48" s="14"/>
-      <c r="P48" s="14" t="s">
+      <c r="P48" t="s">
         <v>28</v>
       </c>
-      <c r="Q48" s="14"/>
-      <c r="R48" s="14" t="s">
+      <c r="R48" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8345,7 +8292,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>173</v>
       </c>
@@ -8395,7 +8342,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>182</v>
       </c>
@@ -8439,7 +8386,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>182</v>
       </c>
@@ -8586,7 +8533,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>194</v>
       </c>
@@ -8639,7 +8586,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>196</v>
       </c>
@@ -8683,7 +8630,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>196</v>
       </c>
@@ -8728,106 +8675,102 @@
       </c>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A58" s="14">
+      <c r="A58">
         <v>195</v>
       </c>
-      <c r="B58" s="14" t="s">
+      <c r="B58" t="s">
         <v>67</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" t="s">
         <v>198</v>
       </c>
-      <c r="D58" s="14" t="s">
+      <c r="D58" t="s">
         <v>352</v>
       </c>
-      <c r="E58" s="14" t="s">
+      <c r="E58" t="s">
         <v>69</v>
       </c>
-      <c r="F58" s="14" t="s">
+      <c r="F58" t="s">
         <v>70</v>
       </c>
-      <c r="G58" s="14" t="s">
+      <c r="G58" t="s">
         <v>21</v>
       </c>
-      <c r="H58" s="15">
+      <c r="H58" s="5">
         <v>45944</v>
       </c>
-      <c r="I58" s="14" t="s">
+      <c r="I58" t="s">
         <v>71</v>
       </c>
-      <c r="J58" s="14" t="s">
+      <c r="J58" t="s">
         <v>199</v>
       </c>
-      <c r="K58" s="14">
+      <c r="K58">
         <v>5</v>
       </c>
-      <c r="L58" s="14" t="s">
+      <c r="L58" t="s">
         <v>73</v>
       </c>
-      <c r="M58" s="14"/>
-      <c r="N58" s="14" t="s">
+      <c r="N58" t="s">
         <v>74</v>
       </c>
-      <c r="O58" s="14" t="s">
+      <c r="O58" t="s">
         <v>200</v>
       </c>
-      <c r="P58" s="14" t="s">
+      <c r="P58" t="s">
         <v>28</v>
       </c>
-      <c r="Q58" s="14"/>
-      <c r="R58" s="14" t="s">
+      <c r="R58" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="59" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A59" s="14">
+      <c r="A59">
         <v>200</v>
       </c>
-      <c r="B59" s="14" t="s">
+      <c r="B59" t="s">
         <v>67</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" t="s">
         <v>193</v>
       </c>
-      <c r="D59" s="14" t="s">
+      <c r="D59" t="s">
         <v>352</v>
       </c>
-      <c r="E59" s="14" t="s">
+      <c r="E59" t="s">
         <v>194</v>
       </c>
-      <c r="F59" s="14" t="s">
+      <c r="F59" t="s">
         <v>195</v>
       </c>
-      <c r="G59" s="14" t="s">
+      <c r="G59" t="s">
         <v>21</v>
       </c>
-      <c r="H59" s="15">
+      <c r="H59" s="5">
         <v>45945</v>
       </c>
-      <c r="I59" s="14" t="s">
+      <c r="I59" t="s">
         <v>71</v>
       </c>
-      <c r="J59" s="14" t="s">
+      <c r="J59" t="s">
         <v>196</v>
       </c>
-      <c r="K59" s="14">
+      <c r="K59">
         <v>5</v>
       </c>
-      <c r="L59" s="14" t="s">
+      <c r="L59" t="s">
         <v>73</v>
       </c>
-      <c r="M59" s="14"/>
-      <c r="N59" s="14" t="s">
+      <c r="N59" t="s">
         <v>74</v>
       </c>
-      <c r="O59" s="14" t="s">
+      <c r="O59" t="s">
         <v>197</v>
       </c>
-      <c r="P59" s="14" t="s">
+      <c r="P59" t="s">
         <v>28</v>
       </c>
-      <c r="Q59" s="14"/>
-      <c r="R59" s="14" t="s">
+      <c r="R59" t="s">
         <v>39</v>
       </c>
     </row>
@@ -8991,58 +8934,56 @@
       </c>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A63" s="14">
+      <c r="A63">
         <v>204</v>
       </c>
-      <c r="B63" s="14" t="s">
+      <c r="B63" t="s">
         <v>67</v>
       </c>
-      <c r="C63" s="14" t="s">
+      <c r="C63" t="s">
         <v>179</v>
       </c>
-      <c r="D63" s="14" t="s">
+      <c r="D63" t="s">
         <v>352</v>
       </c>
-      <c r="E63" s="14" t="s">
+      <c r="E63" t="s">
         <v>69</v>
       </c>
-      <c r="F63" s="14" t="s">
+      <c r="F63" t="s">
         <v>70</v>
       </c>
-      <c r="G63" s="14" t="s">
+      <c r="G63" t="s">
         <v>21</v>
       </c>
-      <c r="H63" s="15">
+      <c r="H63" s="5">
         <v>45946</v>
       </c>
-      <c r="I63" s="14" t="s">
+      <c r="I63" t="s">
         <v>71</v>
       </c>
-      <c r="J63" s="14" t="s">
+      <c r="J63" t="s">
         <v>180</v>
       </c>
-      <c r="K63" s="14">
+      <c r="K63">
         <v>5</v>
       </c>
-      <c r="L63" s="14" t="s">
+      <c r="L63" t="s">
         <v>73</v>
       </c>
-      <c r="M63" s="14"/>
-      <c r="N63" s="14" t="s">
+      <c r="N63" t="s">
         <v>74</v>
       </c>
-      <c r="O63" s="14" t="s">
+      <c r="O63" t="s">
         <v>181</v>
       </c>
-      <c r="P63" s="14" t="s">
+      <c r="P63" t="s">
         <v>28</v>
       </c>
-      <c r="Q63" s="14"/>
-      <c r="R63" s="14" t="s">
+      <c r="R63" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>207</v>
       </c>
@@ -9095,165 +9036,160 @@
         <v>29</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A65" s="14">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A65">
         <v>209</v>
       </c>
-      <c r="B65" s="14" t="s">
+      <c r="B65" t="s">
         <v>67</v>
       </c>
-      <c r="C65" s="14" t="s">
+      <c r="C65" t="s">
         <v>173</v>
       </c>
-      <c r="D65" s="14" t="s">
+      <c r="D65" t="s">
         <v>352</v>
       </c>
-      <c r="E65" s="14" t="s">
+      <c r="E65" t="s">
         <v>69</v>
       </c>
-      <c r="F65" s="14" t="s">
+      <c r="F65" t="s">
         <v>70</v>
       </c>
-      <c r="G65" s="14" t="s">
+      <c r="G65" t="s">
         <v>21</v>
       </c>
-      <c r="H65" s="15">
+      <c r="H65" s="5">
         <v>45947</v>
       </c>
-      <c r="I65" s="14" t="s">
+      <c r="I65" t="s">
         <v>71</v>
       </c>
-      <c r="J65" s="14" t="s">
+      <c r="J65" t="s">
         <v>174</v>
       </c>
-      <c r="K65" s="14">
+      <c r="K65">
         <v>5</v>
       </c>
-      <c r="L65" s="14" t="s">
+      <c r="L65" t="s">
         <v>73</v>
       </c>
-      <c r="M65" s="14"/>
-      <c r="N65" s="14" t="s">
+      <c r="N65" t="s">
         <v>74</v>
       </c>
-      <c r="O65" s="14" t="s">
+      <c r="O65" t="s">
         <v>175</v>
       </c>
-      <c r="P65" s="14" t="s">
+      <c r="P65" t="s">
         <v>28</v>
       </c>
-      <c r="Q65" s="14"/>
-      <c r="R65" s="14" t="s">
+      <c r="R65" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A66" s="14">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A66">
         <v>212</v>
       </c>
-      <c r="B66" s="14" t="s">
+      <c r="B66" t="s">
         <v>67</v>
       </c>
-      <c r="C66" s="14" t="s">
+      <c r="C66" t="s">
         <v>164</v>
       </c>
-      <c r="D66" s="14" t="s">
+      <c r="D66" t="s">
         <v>352</v>
       </c>
-      <c r="E66" s="14" t="s">
+      <c r="E66" t="s">
         <v>69</v>
       </c>
-      <c r="F66" s="14" t="s">
+      <c r="F66" t="s">
         <v>70</v>
       </c>
-      <c r="G66" s="14" t="s">
+      <c r="G66" t="s">
         <v>21</v>
       </c>
-      <c r="H66" s="15">
+      <c r="H66" s="5">
         <v>45947</v>
       </c>
-      <c r="I66" s="14" t="s">
+      <c r="I66" t="s">
         <v>71</v>
       </c>
-      <c r="J66" s="14" t="s">
+      <c r="J66" t="s">
         <v>165</v>
       </c>
-      <c r="K66" s="14">
+      <c r="K66">
         <v>5</v>
       </c>
-      <c r="L66" s="14" t="s">
+      <c r="L66" t="s">
         <v>73</v>
       </c>
-      <c r="M66" s="14"/>
-      <c r="N66" s="14" t="s">
+      <c r="N66" t="s">
         <v>74</v>
       </c>
-      <c r="O66" s="14" t="s">
+      <c r="O66" t="s">
         <v>166</v>
       </c>
-      <c r="P66" s="14" t="s">
+      <c r="P66" t="s">
         <v>28</v>
       </c>
-      <c r="Q66" s="14"/>
-      <c r="R66" s="14" t="s">
+      <c r="R66" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="365" x14ac:dyDescent="0.2">
-      <c r="A67" s="14">
+    <row r="67" spans="1:18" ht="365" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A67">
         <v>210</v>
       </c>
-      <c r="B67" s="14" t="s">
+      <c r="B67" t="s">
         <v>30</v>
       </c>
-      <c r="C67" s="14" t="s">
+      <c r="C67" t="s">
         <v>167</v>
       </c>
-      <c r="D67" s="14" t="s">
+      <c r="D67" t="s">
         <v>429</v>
       </c>
-      <c r="E67" s="14" t="s">
+      <c r="E67" t="s">
         <v>168</v>
       </c>
-      <c r="F67" s="14" t="s">
+      <c r="F67" t="s">
         <v>169</v>
       </c>
-      <c r="G67" s="14" t="s">
+      <c r="G67" t="s">
         <v>21</v>
       </c>
-      <c r="H67" s="15">
+      <c r="H67" s="5">
         <v>45947</v>
       </c>
-      <c r="I67" s="14" t="s">
+      <c r="I67" t="s">
         <v>142</v>
       </c>
-      <c r="J67" s="16" t="s">
+      <c r="J67" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="K67" s="14">
+      <c r="K67">
         <v>5</v>
       </c>
-      <c r="L67" s="14" t="s">
+      <c r="L67" t="s">
         <v>24</v>
       </c>
-      <c r="M67" s="14" t="s">
+      <c r="M67" t="s">
         <v>171</v>
       </c>
-      <c r="N67" s="14" t="s">
+      <c r="N67" t="s">
         <v>172</v>
       </c>
-      <c r="O67" s="14" t="s">
+      <c r="O67" t="s">
         <v>61</v>
       </c>
-      <c r="P67" s="14" t="s">
+      <c r="P67" t="s">
         <v>28</v>
       </c>
-      <c r="Q67" s="14"/>
-      <c r="R67" s="14" t="s">
+      <c r="R67" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>216</v>
       </c>
@@ -9300,7 +9236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>220</v>
       </c>
@@ -9347,7 +9283,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>224</v>
       </c>
@@ -9391,7 +9327,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>226</v>
       </c>
@@ -9438,7 +9374,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>229</v>
       </c>
@@ -9486,56 +9422,53 @@
       </c>
     </row>
     <row r="73" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A73" s="14">
+      <c r="A73">
         <v>244</v>
       </c>
-      <c r="B73" s="14" t="s">
+      <c r="B73" t="s">
         <v>145</v>
       </c>
-      <c r="C73" s="14" t="s">
+      <c r="C73" t="s">
         <v>146</v>
       </c>
-      <c r="D73" s="14" t="s">
+      <c r="D73" t="s">
         <v>427</v>
       </c>
-      <c r="E73" s="14" t="s">
+      <c r="E73" t="s">
         <v>132</v>
       </c>
-      <c r="F73" s="14" t="s">
+      <c r="F73" t="s">
         <v>133</v>
       </c>
-      <c r="G73" s="14" t="s">
+      <c r="G73" t="s">
         <v>21</v>
       </c>
-      <c r="H73" s="15">
+      <c r="H73" s="5">
         <v>45965</v>
       </c>
-      <c r="I73" s="14" t="s">
+      <c r="I73" t="s">
         <v>147</v>
       </c>
-      <c r="J73" s="14" t="s">
+      <c r="J73" t="s">
         <v>148</v>
       </c>
-      <c r="K73" s="14">
+      <c r="K73">
         <v>5</v>
       </c>
-      <c r="L73" s="14" t="s">
+      <c r="L73" t="s">
         <v>35</v>
       </c>
-      <c r="M73" s="14"/>
-      <c r="N73" s="14"/>
-      <c r="O73" s="14" t="s">
+      <c r="O73" t="s">
         <v>149</v>
       </c>
-      <c r="P73" s="14" t="s">
+      <c r="P73" t="s">
         <v>28</v>
       </c>
-      <c r="Q73" s="14"/>
-      <c r="R73" s="14" t="s">
+      <c r="R73" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>253</v>
       </c>
@@ -9579,7 +9512,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>253</v>
       </c>
@@ -9668,110 +9601,108 @@
       </c>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A77" s="14">
+      <c r="A77">
         <v>257</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B77" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="14" t="s">
+      <c r="C77" t="s">
         <v>141</v>
       </c>
-      <c r="D77" s="14" t="s">
+      <c r="D77" t="s">
         <v>429</v>
       </c>
-      <c r="E77" s="14" t="s">
+      <c r="E77" t="s">
         <v>19</v>
       </c>
-      <c r="F77" s="14" t="s">
+      <c r="F77" t="s">
         <v>80</v>
       </c>
-      <c r="G77" s="14" t="s">
+      <c r="G77" t="s">
         <v>21</v>
       </c>
-      <c r="H77" s="15">
+      <c r="H77" s="5">
         <v>45971</v>
       </c>
-      <c r="I77" s="14" t="s">
+      <c r="I77" t="s">
         <v>142</v>
       </c>
-      <c r="J77" s="14" t="s">
+      <c r="J77" t="s">
         <v>143</v>
       </c>
-      <c r="K77" s="14">
+      <c r="K77">
         <v>5</v>
       </c>
-      <c r="L77" s="14" t="s">
+      <c r="L77" t="s">
         <v>73</v>
       </c>
-      <c r="M77" s="14" t="s">
+      <c r="M77" t="s">
         <v>61</v>
       </c>
-      <c r="N77" s="14" t="s">
+      <c r="N77" t="s">
         <v>74</v>
       </c>
-      <c r="O77" s="14" t="s">
+      <c r="O77" t="s">
         <v>144</v>
       </c>
-      <c r="P77" s="14" t="s">
+      <c r="P77" t="s">
         <v>28</v>
       </c>
-      <c r="Q77" s="14"/>
-      <c r="R77" s="14" t="s">
+      <c r="R77" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A78" s="14">
+      <c r="A78">
         <v>257</v>
       </c>
-      <c r="B78" s="14" t="s">
+      <c r="B78" t="s">
         <v>30</v>
       </c>
-      <c r="C78" s="14" t="s">
+      <c r="C78" t="s">
         <v>141</v>
       </c>
-      <c r="D78" s="14" t="s">
+      <c r="D78" t="s">
         <v>429</v>
       </c>
-      <c r="E78" s="14" t="s">
+      <c r="E78" t="s">
         <v>19</v>
       </c>
-      <c r="F78" s="14" t="s">
+      <c r="F78" t="s">
         <v>20</v>
       </c>
-      <c r="G78" s="14" t="s">
+      <c r="G78" t="s">
         <v>21</v>
       </c>
-      <c r="H78" s="15">
+      <c r="H78" s="5">
         <v>45971</v>
       </c>
-      <c r="I78" s="14" t="s">
+      <c r="I78" t="s">
         <v>142</v>
       </c>
-      <c r="J78" s="14" t="s">
+      <c r="J78" t="s">
         <v>143</v>
       </c>
-      <c r="K78" s="14">
+      <c r="K78">
         <v>5</v>
       </c>
-      <c r="L78" s="14" t="s">
+      <c r="L78" t="s">
         <v>73</v>
       </c>
-      <c r="M78" s="14" t="s">
+      <c r="M78" t="s">
         <v>61</v>
       </c>
-      <c r="N78" s="14" t="s">
+      <c r="N78" t="s">
         <v>74</v>
       </c>
-      <c r="O78" s="14" t="s">
+      <c r="O78" t="s">
         <v>61</v>
       </c>
-      <c r="P78" s="14" t="s">
+      <c r="P78" t="s">
         <v>28</v>
       </c>
-      <c r="Q78" s="14"/>
-      <c r="R78" s="14" t="s">
+      <c r="R78" t="s">
         <v>39</v>
       </c>
     </row>
@@ -9829,60 +9760,59 @@
       </c>
     </row>
     <row r="80" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A80" s="14">
+      <c r="A80">
         <v>260</v>
       </c>
-      <c r="B80" s="14" t="s">
+      <c r="B80" t="s">
         <v>130</v>
       </c>
-      <c r="C80" s="14" t="s">
+      <c r="C80" t="s">
         <v>131</v>
       </c>
-      <c r="D80" s="14" t="s">
+      <c r="D80" t="s">
         <v>427</v>
       </c>
-      <c r="E80" s="14" t="s">
+      <c r="E80" t="s">
         <v>132</v>
       </c>
-      <c r="F80" s="14" t="s">
+      <c r="F80" t="s">
         <v>133</v>
       </c>
-      <c r="G80" s="14" t="s">
+      <c r="G80" t="s">
         <v>21</v>
       </c>
-      <c r="H80" s="15">
+      <c r="H80" s="5">
         <v>45972</v>
       </c>
-      <c r="I80" s="14" t="s">
+      <c r="I80" t="s">
         <v>134</v>
       </c>
-      <c r="J80" s="14" t="s">
+      <c r="J80" t="s">
         <v>135</v>
       </c>
-      <c r="K80" s="14">
+      <c r="K80">
         <v>5</v>
       </c>
-      <c r="L80" s="14" t="s">
+      <c r="L80" t="s">
         <v>35</v>
       </c>
-      <c r="M80" s="14" t="s">
+      <c r="M80" t="s">
         <v>139</v>
       </c>
-      <c r="N80" s="14" t="s">
+      <c r="N80" t="s">
         <v>140</v>
       </c>
-      <c r="O80" s="14" t="s">
+      <c r="O80" t="s">
         <v>140</v>
       </c>
-      <c r="P80" s="14" t="s">
+      <c r="P80" t="s">
         <v>28</v>
       </c>
-      <c r="Q80" s="14"/>
-      <c r="R80" s="14" t="s">
+      <c r="R80" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>263</v>
       </c>
@@ -9935,7 +9865,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>270</v>
       </c>
@@ -9988,7 +9918,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>280</v>
       </c>
@@ -10041,7 +9971,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>280</v>
       </c>
@@ -10094,7 +10024,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>277</v>
       </c>
@@ -10147,61 +10077,60 @@
         <v>29</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A86" s="14">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A86">
         <v>280</v>
       </c>
-      <c r="B86" s="14" t="s">
+      <c r="B86" t="s">
         <v>30</v>
       </c>
-      <c r="C86" s="14" t="s">
+      <c r="C86" t="s">
         <v>53</v>
       </c>
-      <c r="D86" s="14" t="s">
+      <c r="D86" t="s">
         <v>429</v>
       </c>
-      <c r="E86" s="14" t="s">
+      <c r="E86" t="s">
         <v>19</v>
       </c>
-      <c r="F86" s="14" t="s">
+      <c r="F86" t="s">
         <v>93</v>
       </c>
-      <c r="G86" s="14" t="s">
+      <c r="G86" t="s">
         <v>21</v>
       </c>
-      <c r="H86" s="15">
+      <c r="H86" s="5">
         <v>45980</v>
       </c>
-      <c r="I86" s="14" t="s">
+      <c r="I86" t="s">
         <v>81</v>
       </c>
-      <c r="J86" s="14" t="s">
+      <c r="J86" t="s">
         <v>94</v>
       </c>
-      <c r="K86" s="14">
+      <c r="K86">
         <v>5</v>
       </c>
-      <c r="L86" s="14" t="s">
+      <c r="L86" t="s">
         <v>24</v>
       </c>
-      <c r="M86" s="14" t="s">
+      <c r="M86" t="s">
         <v>25</v>
       </c>
-      <c r="N86" s="14" t="s">
+      <c r="N86" t="s">
         <v>95</v>
       </c>
-      <c r="O86" s="14" t="s">
+      <c r="O86" t="s">
         <v>96</v>
       </c>
-      <c r="P86" s="14" t="s">
+      <c r="P86" t="s">
         <v>28</v>
       </c>
-      <c r="Q86" s="14"/>
-      <c r="R86" s="14" t="s">
+      <c r="R86" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>281</v>
       </c>
@@ -10254,7 +10183,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>281</v>
       </c>
@@ -10307,7 +10236,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>281</v>
       </c>
@@ -10360,7 +10289,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>281</v>
       </c>
@@ -10464,58 +10393,56 @@
       </c>
     </row>
     <row r="92" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A92" s="14">
+      <c r="A92">
         <v>286</v>
       </c>
-      <c r="B92" s="14" t="s">
+      <c r="B92" t="s">
         <v>67</v>
       </c>
-      <c r="C92" s="14" t="s">
+      <c r="C92" t="s">
         <v>68</v>
       </c>
-      <c r="D92" s="14" t="s">
+      <c r="D92" t="s">
         <v>352</v>
       </c>
-      <c r="E92" s="14" t="s">
+      <c r="E92" t="s">
         <v>69</v>
       </c>
-      <c r="F92" s="14" t="s">
+      <c r="F92" t="s">
         <v>70</v>
       </c>
-      <c r="G92" s="14" t="s">
+      <c r="G92" t="s">
         <v>21</v>
       </c>
-      <c r="H92" s="15">
+      <c r="H92" s="5">
         <v>45982</v>
       </c>
-      <c r="I92" s="14" t="s">
+      <c r="I92" t="s">
         <v>71</v>
       </c>
-      <c r="J92" s="14" t="s">
+      <c r="J92" t="s">
         <v>72</v>
       </c>
-      <c r="K92" s="14">
+      <c r="K92">
         <v>5</v>
       </c>
-      <c r="L92" s="14" t="s">
+      <c r="L92" t="s">
         <v>73</v>
       </c>
-      <c r="M92" s="14"/>
-      <c r="N92" s="14" t="s">
+      <c r="N92" t="s">
         <v>74</v>
       </c>
-      <c r="O92" s="14" t="s">
+      <c r="O92" t="s">
         <v>75</v>
       </c>
-      <c r="P92" s="14" t="s">
+      <c r="P92" t="s">
         <v>28</v>
       </c>
-      <c r="Q92" s="14"/>
-      <c r="R92" s="14" t="s">
+      <c r="R92" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>291</v>
       </c>
@@ -10568,7 +10495,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>291</v>
       </c>
@@ -10621,7 +10548,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>287</v>
       </c>
@@ -10665,61 +10592,60 @@
         <v>29</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A96" s="14">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A96">
         <v>289</v>
       </c>
-      <c r="B96" s="14" t="s">
+      <c r="B96" t="s">
         <v>17</v>
       </c>
-      <c r="C96" s="14" t="s">
+      <c r="C96" t="s">
         <v>62</v>
       </c>
-      <c r="D96" s="14" t="s">
+      <c r="D96" t="s">
         <v>429</v>
       </c>
-      <c r="E96" s="14" t="s">
+      <c r="E96" t="s">
         <v>19</v>
       </c>
-      <c r="F96" s="14" t="s">
+      <c r="F96" t="s">
         <v>63</v>
       </c>
-      <c r="G96" s="14" t="s">
+      <c r="G96" t="s">
         <v>21</v>
       </c>
-      <c r="H96" s="15">
+      <c r="H96" s="5">
         <v>45985</v>
       </c>
-      <c r="I96" s="14" t="s">
+      <c r="I96" t="s">
         <v>22</v>
       </c>
-      <c r="J96" s="14" t="s">
+      <c r="J96" t="s">
         <v>64</v>
       </c>
-      <c r="K96" s="14">
+      <c r="K96">
         <v>5</v>
       </c>
-      <c r="L96" s="14" t="s">
+      <c r="L96" t="s">
         <v>24</v>
       </c>
-      <c r="M96" s="14" t="s">
+      <c r="M96" t="s">
         <v>25</v>
       </c>
-      <c r="N96" s="14" t="s">
+      <c r="N96" t="s">
         <v>65</v>
       </c>
-      <c r="O96" s="14" t="s">
+      <c r="O96" t="s">
         <v>66</v>
       </c>
-      <c r="P96" s="14" t="s">
+      <c r="P96" t="s">
         <v>28</v>
       </c>
-      <c r="Q96" s="14"/>
-      <c r="R96" s="14" t="s">
+      <c r="R96" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>293</v>
       </c>
@@ -10772,7 +10698,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>293</v>
       </c>
@@ -10825,7 +10751,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>293</v>
       </c>
@@ -10878,7 +10804,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>293</v>
       </c>
@@ -10931,7 +10857,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>290</v>
       </c>
@@ -10975,7 +10901,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>290</v>
       </c>
@@ -11019,163 +10945,157 @@
         <v>39</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A103" s="14">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A103">
         <v>293</v>
       </c>
-      <c r="B103" s="14" t="s">
+      <c r="B103" t="s">
         <v>30</v>
       </c>
-      <c r="C103" s="14" t="s">
+      <c r="C103" t="s">
         <v>31</v>
       </c>
-      <c r="D103" s="14" t="s">
+      <c r="D103" t="s">
         <v>429</v>
       </c>
-      <c r="E103" s="14" t="s">
+      <c r="E103" t="s">
         <v>19</v>
       </c>
-      <c r="F103" s="14" t="s">
+      <c r="F103" t="s">
         <v>40</v>
       </c>
-      <c r="G103" s="14" t="s">
+      <c r="G103" t="s">
         <v>21</v>
       </c>
-      <c r="H103" s="15">
+      <c r="H103" s="5">
         <v>45986</v>
       </c>
-      <c r="I103" s="14" t="s">
+      <c r="I103" t="s">
         <v>33</v>
       </c>
-      <c r="J103" s="14" t="s">
+      <c r="J103" t="s">
         <v>41</v>
       </c>
-      <c r="K103" s="14">
+      <c r="K103">
         <v>5</v>
       </c>
-      <c r="L103" s="14" t="s">
+      <c r="L103" t="s">
         <v>24</v>
       </c>
-      <c r="M103" s="14" t="s">
+      <c r="M103" t="s">
         <v>42</v>
       </c>
-      <c r="N103" s="14" t="s">
+      <c r="N103" t="s">
         <v>43</v>
       </c>
-      <c r="O103" s="14" t="s">
+      <c r="O103" t="s">
         <v>38</v>
       </c>
-      <c r="P103" s="14" t="s">
+      <c r="P103" t="s">
         <v>28</v>
       </c>
-      <c r="Q103" s="14"/>
-      <c r="R103" s="14" t="s">
+      <c r="R103" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A104" s="14">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A104">
         <v>293</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" t="s">
         <v>30</v>
       </c>
-      <c r="C104" s="14" t="s">
+      <c r="C104" t="s">
         <v>31</v>
       </c>
-      <c r="D104" s="14" t="s">
+      <c r="D104" t="s">
         <v>429</v>
       </c>
-      <c r="E104" s="14" t="s">
+      <c r="E104" t="s">
         <v>19</v>
       </c>
-      <c r="F104" s="14" t="s">
+      <c r="F104" t="s">
         <v>49</v>
       </c>
-      <c r="G104" s="14" t="s">
+      <c r="G104" t="s">
         <v>21</v>
       </c>
-      <c r="H104" s="15">
+      <c r="H104" s="5">
         <v>45986</v>
       </c>
-      <c r="I104" s="14" t="s">
+      <c r="I104" t="s">
         <v>33</v>
       </c>
-      <c r="J104" s="14" t="s">
+      <c r="J104" t="s">
         <v>41</v>
       </c>
-      <c r="K104" s="14">
+      <c r="K104">
         <v>5</v>
       </c>
-      <c r="L104" s="14" t="s">
+      <c r="L104" t="s">
         <v>24</v>
       </c>
-      <c r="M104" s="14" t="s">
+      <c r="M104" t="s">
         <v>42</v>
       </c>
-      <c r="N104" s="14" t="s">
+      <c r="N104" t="s">
         <v>50</v>
       </c>
-      <c r="O104" s="14" t="s">
+      <c r="O104" t="s">
         <v>38</v>
       </c>
-      <c r="P104" s="14" t="s">
+      <c r="P104" t="s">
         <v>28</v>
       </c>
-      <c r="Q104" s="14"/>
-      <c r="R104" s="14" t="s">
+      <c r="R104" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A105" s="14">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A105">
         <v>310</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" t="s">
         <v>365</v>
       </c>
-      <c r="C105" s="14" t="s">
+      <c r="C105" t="s">
         <v>417</v>
       </c>
-      <c r="D105" s="14" t="s">
+      <c r="D105" t="s">
         <v>430</v>
       </c>
-      <c r="E105" s="14" t="s">
+      <c r="E105" t="s">
         <v>411</v>
       </c>
-      <c r="F105" s="14" t="s">
+      <c r="F105" t="s">
         <v>412</v>
       </c>
-      <c r="G105" s="14" t="s">
+      <c r="G105" t="s">
         <v>381</v>
       </c>
-      <c r="H105" s="15">
+      <c r="H105" s="5">
         <v>45986</v>
       </c>
-      <c r="I105" s="14" t="s">
+      <c r="I105" t="s">
         <v>420</v>
       </c>
-      <c r="J105" s="14" t="s">
+      <c r="J105" t="s">
         <v>414</v>
       </c>
-      <c r="K105" s="14">
+      <c r="K105">
         <v>5</v>
       </c>
-      <c r="L105" s="14"/>
-      <c r="M105" s="14"/>
-      <c r="N105" s="14"/>
-      <c r="O105" s="14"/>
-      <c r="P105" s="14" t="s">
+      <c r="P105" t="s">
         <v>384</v>
       </c>
-      <c r="Q105" s="14" t="s">
+      <c r="Q105" t="s">
         <v>21</v>
       </c>
-      <c r="R105" s="14" t="s">
+      <c r="R105" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>304</v>
       </c>
@@ -11228,51 +11148,47 @@
         <v>39</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A107" s="14">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A107">
         <v>334</v>
       </c>
-      <c r="B107" s="14" t="s">
+      <c r="B107" t="s">
         <v>130</v>
       </c>
-      <c r="C107" s="14" t="s">
+      <c r="C107" t="s">
         <v>418</v>
       </c>
-      <c r="D107" s="14" t="s">
+      <c r="D107" t="s">
         <v>427</v>
       </c>
-      <c r="E107" s="14" t="s">
+      <c r="E107" t="s">
         <v>132</v>
       </c>
-      <c r="F107" s="14" t="s">
+      <c r="F107" t="s">
         <v>413</v>
       </c>
-      <c r="G107" s="14" t="s">
+      <c r="G107" t="s">
         <v>381</v>
       </c>
-      <c r="H107" s="15">
+      <c r="H107" s="5">
         <v>46006</v>
       </c>
-      <c r="I107" s="14" t="s">
+      <c r="I107" t="s">
         <v>134</v>
       </c>
-      <c r="J107" s="14" t="s">
+      <c r="J107" t="s">
         <v>415</v>
       </c>
-      <c r="K107" s="14">
+      <c r="K107">
         <v>5</v>
       </c>
-      <c r="L107" s="14"/>
-      <c r="M107" s="14"/>
-      <c r="N107" s="14"/>
-      <c r="O107" s="14"/>
-      <c r="P107" s="14" t="s">
+      <c r="P107" t="s">
         <v>384</v>
       </c>
-      <c r="Q107" s="14" t="s">
+      <c r="Q107" t="s">
         <v>21</v>
       </c>
-      <c r="R107" s="14" t="s">
+      <c r="R107" t="s">
         <v>39</v>
       </c>
     </row>
@@ -11368,136 +11284,192 @@
         <v>39</v>
       </c>
     </row>
-    <row r="110" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="14">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A110">
         <v>349</v>
       </c>
-      <c r="B110" s="14" t="s">
+      <c r="B110" t="s">
         <v>377</v>
       </c>
-      <c r="C110" s="14" t="s">
+      <c r="C110" t="s">
         <v>440</v>
       </c>
-      <c r="D110" s="14" t="s">
+      <c r="D110" t="s">
         <v>429</v>
       </c>
-      <c r="E110" s="14" t="s">
+      <c r="E110" t="s">
         <v>436</v>
       </c>
-      <c r="F110" s="14" t="s">
+      <c r="F110" t="s">
         <v>437</v>
       </c>
-      <c r="G110" s="14" t="s">
+      <c r="G110" t="s">
         <v>381</v>
       </c>
-      <c r="H110" s="15">
+      <c r="H110" s="5">
         <v>46014</v>
       </c>
-      <c r="J110" s="14" t="s">
+      <c r="J110" t="s">
         <v>442</v>
       </c>
-      <c r="R110" s="14" t="s">
+      <c r="R110" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="111" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="14">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A111">
         <v>356</v>
       </c>
-      <c r="B111" s="14" t="s">
+      <c r="B111" t="s">
         <v>377</v>
       </c>
-      <c r="C111" s="14" t="s">
+      <c r="C111" t="s">
         <v>441</v>
       </c>
-      <c r="D111" s="14" t="s">
+      <c r="D111" t="s">
         <v>429</v>
       </c>
-      <c r="E111" s="14" t="s">
+      <c r="E111" t="s">
         <v>19</v>
       </c>
-      <c r="F111" s="14" t="s">
+      <c r="F111" t="s">
         <v>438</v>
       </c>
-      <c r="G111" s="14" t="s">
+      <c r="G111" t="s">
         <v>381</v>
       </c>
-      <c r="H111" s="15">
+      <c r="H111" s="5">
         <v>46015</v>
       </c>
-      <c r="J111" s="14" t="s">
+      <c r="J111" t="s">
         <v>443</v>
       </c>
-      <c r="R111" s="14" t="s">
+      <c r="R111" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="112" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="14">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A112">
         <v>357</v>
       </c>
-      <c r="B112" s="14" t="s">
+      <c r="B112" t="s">
         <v>145</v>
       </c>
-      <c r="C112" s="14" t="s">
+      <c r="C112" t="s">
         <v>282</v>
       </c>
-      <c r="D112" s="14" t="s">
+      <c r="D112" t="s">
         <v>427</v>
       </c>
-      <c r="E112" s="14" t="s">
+      <c r="E112" t="s">
         <v>391</v>
       </c>
-      <c r="F112" s="14" t="s">
+      <c r="F112" t="s">
         <v>439</v>
       </c>
-      <c r="G112" s="14" t="s">
+      <c r="G112" t="s">
         <v>381</v>
       </c>
-      <c r="H112" s="15">
+      <c r="H112" s="5">
         <v>46020</v>
       </c>
-      <c r="J112" s="14" t="s">
+      <c r="J112" t="s">
         <v>444</v>
       </c>
-      <c r="R112" s="14" t="s">
+      <c r="R112" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="113" spans="1:18" s="14" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="14">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A113">
         <v>357</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" t="s">
         <v>145</v>
       </c>
-      <c r="C113" s="14" t="s">
+      <c r="C113" t="s">
         <v>282</v>
       </c>
-      <c r="D113" s="14" t="s">
+      <c r="D113" t="s">
         <v>427</v>
       </c>
-      <c r="E113" s="14" t="s">
+      <c r="E113" t="s">
         <v>391</v>
       </c>
-      <c r="F113" s="14" t="s">
+      <c r="F113" t="s">
         <v>439</v>
       </c>
-      <c r="G113" s="14" t="s">
+      <c r="G113" t="s">
         <v>381</v>
       </c>
-      <c r="H113" s="15">
+      <c r="H113" s="5">
         <v>46020</v>
       </c>
-      <c r="J113" s="14" t="s">
+      <c r="J113" t="s">
         <v>445</v>
       </c>
-      <c r="R113" s="14" t="s">
+      <c r="R113" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R109" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <autoFilter xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" ref="A1:R113" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="9">
+      <filters>
+        <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+          <mc:Choice Requires="x14">
+            <x14:filter val="-Se canaliza, cablea y conecta modbus caudalimetro coagulante zona 1_x000a_-Se realiza levantamiento de equipos a monitoreo, vdf's, se revisa tablero en el cual se realizará el control._x000a_-Se revisa punto caido en zona 2 el cual se informa que por operador de planta puede ser debido a que se instalo caseta nueva en el recinto y se tuvo que mover la canalización de esta quedando el cable tirante._x000a_-Se revisa telemetria de zona 1 antes de la nueva implementacion la cual se va a mejorar antes de generar nuevo programa._x000a_-Bomba a leer del floculante fue retirada se instalo una provisoria la cual no es posible leer ya que es básica."/>
+            <x14:filter val="-Se logran leer vdf que no se pudieron en vez anterior, solo llega un dato por ahora lo que quiere decir que configuración del equipo y conexión estan ok._x000a_- Se canaliza a vdf de bomba daf para leer estado._x000a_-Se canalizan y cablea casi al 90% zona 1 _x000a_-Adicional se cambia rutina modbus zona 1 leyendo equipos anteriores de forma mas robusta por parte de Matias Pomar"/>
+            <x14:filter val="-Se realiza montaje, canalizacion y cableado de We-connect para alimentación del tablero desde tablero auxiliar y canalización y cableado a flujometro Mag5000. _x000a_-Flujometro tiene Salida digital ocupada por controlador que se utiliza para controlar por m3 bombas de impulsion hacia Biodiversa._x000a_Salida analógica esta utilizada por equipo de lectura por parte de Biodiversa el cual es visualizado a diario por operador._x000a_-Se realizan pruebas de lectura de Mag5000 con UC300 (telemetria) dejando fuera control del cliente con resultados positivos  leyendo Volumen a la par, caudal de aprox 5,7 l/s  20,5m3/h._x000a_ Por motivos de que es de importancia para el control de las bombas la lectura digital del Volumen se vuelve atrás instalación de We-techs, por lo cual solo la telemetria queda fuera, tablero y canalizaciones ok._x000a__x000a_Se realiza levantamiento de estado de la instalación, verificación de fuente de alimentación es de 24VAC para conteo de pulsos de parte cliente con su controlador, lo cual que en caso de requerir utilizar esta fuente de alimentación para duplicar señal con UC 300 es incompatible ya que este equipo es de VCC._x000a__x000a_Adicional se realiza levantamiento en planta Biodiversa donde bomba DDI grundfos del fluctuante fue cambiado por otra bomba se adjunta imagen en OT, en este caso era solo cambiar el conector. Técnico instalo la bomba el dia de hoy, no tenia el manual en información para decirnos que salida disponibles nos puede dejar, y si es intervenida por terceros pierde garantía el equipo."/>
+            <x14:filter val="Adicionales canalizaciones y conexión de TC y PH queda ok._x000a_Validaciones terreno plataforma de PH en ambas zonas ok._x000a_Validación terreno plataforma de caudales y m3 en ambas zonas ok. _x000a_Sensores de H2S se conectan y validan datos en plataforma y terreno. En plataforma marca decimales en terreno no por ende se marca una diferencia de decimal, ejemplo  plataforma 0.3 y terreno 0._x000a_Pruebas de control por plataforma ok control por m3l ok._x000a__x000a_"/>
+            <x14:filter val="Con la Configuración y orientación de antenas en Biodiversa se logra comunicación e tre punto de zona 2 y 1._x000a_Se levantan datos modbus de zona 2 pegados. _x000a_Se incorpora señal nueva de caudalimetro de salida floculante. Zona 2, señal nueva._x000a_Se configura equipo hoboconnect en Viñas de Concha y toro._x000a_Canalización y cableado en zona 1 Biodiversa."/>
+            <x14:filter val="Conexión entre panel solar tablero we conect solar además se canaliza a tablero we nodo Sutron la comunicación y alimentación"/>
+            <x14:filter val="Empresa SS, efectua trabajos en linea matriz de pozo instalando caudalimetro, ventosa y carrete solicitado, ademas de las modificaciones en linea._x000a_Por otra parte, realiza canalizado y conexionado transmisor de pulso caudalimetro hacia tablero nodo lora. Caudalimetro nuevo 10l/p."/>
+            <x14:filter val="Hoy se realizo el montaje del sensor RQ30  en estero el gallo además se realizo canalización a la vista desde equipo hasta tableros._x000a_Montaje de antena con su canalización y cableado. _x000a_Canalización entre tableros._x000a_Canalización hasta el punto donde se conectara la sonda multiparametrica"/>
+            <x14:filter val="Instalacion completa de las estructuras de soportacion de los paneles, montaje de paneles y conexionado entre estos. _x000a__x000a_Canalizaciones en loza y bajada a nivel de suelo para ingreso de la alimentación fotovoltaica a tableros We Techs."/>
+            <x14:filter val="P3G Se realizó la canalización del microtubo, dejando lista la infraestructura hidráulica para el paso del caudal._x000a__x000a_Queda pendiente la integración del equipo Sutron y la conexión de la sonda multiparamétrica HL4. Una vez completada esta etapa, se deberán configurar los parámetros correspondientes para habilitar la transmisión de datos hacia la plataforma._x000a__x000a_Durante el proceso se efectuaron pruebas de verificación mediante el software Hydrolab, que permite la lectura directa de la sonda HL4, y con el software LinkComm, que recibe los registros del equipo Sutron. Estas pruebas confirmaron que el cable de la sonda tiene problemas._x000a__x000a_Sin embargo, se identificó que el cable de la sonda presenta fallas, generando problemas de comunicación al intentar establecer conexión con el software. Este inconveniente deberá resolverse mediante el reemplazo del cable, previo a la validación final y la puesta en marcha del sistema."/>
+            <x14:filter val="P6 Se realizó la canalización del microtubo hacia el cilindro Kase, dejando lista la infraestructura hidráulica para el paso del caudal._x000a__x000a_Queda pendiente la integración del equipo Sutron con su cable de 100 metros, así como la conexión de la sonda multiparamétrica HL4. Una vez completada esta integración, se deberán configurar los parámetros correspondientes para habilitar la transmisión de datos hacia la plataforma."/>
+            <x14:filter val="PBM4 Se realizó la canalización del microtubo hacia el cilindro Kase, dejando lista la infraestructura hidráulica para el paso del caudal._x000a__x000a_Queda pendiente la integración del equipo Sutron con su cable de 100 metros, así como la conexión de la sonda multiparamétrica HL4. Una vez completada esta integración, se deberán configurar los parámetros correspondientes para habilitar la transmisión de datos hacia la plataforma."/>
+            <x14:filter val="Realizamos avances en instalacion de sensores de velocidad, canalización y cableado en estero."/>
+            <x14:filter val="Se deja punto a punto finalizado en zona 1._x000a_Rotulacion de instrumentación en zona 1 ok._x000a_Canalizacion y cableado de quemador 2 ok_x000a_Rotulado de señales de quemador ok._x000a_Se compromete instalación de antena satélital."/>
+            <x14:filter val="Se finaliza en zona 2 canalizaciones y cableado _x000a_En zona 2 mañana se tiene que vanalizar desde vdf decanter a tablero We-connect para leer equipos por teltonika. _x000a_Telemetria de equipos modbus queda fuera por cambios en rutina_x000a_Vdf Daf se verá la última posibilidad de leer el estado de funcionamiento para saber si esta en paralelo o serie."/>
+            <x14:filter val="Se finalizan canalizaciones y conexionado de los paneles además del montaje del inversor y llegada de la alimentación solar al mismo._x000a__x000a_La configuración de la solución solar es mixta siendo 2 grupos de 3 paneles conectados en serie._x000a__x000a_Configuración de parametros en inversor y pruebas de la alimentación con y sin red electrica manteniendo el suministro fotovoltaico de forma permanente._x000a__x000a_Cabe indicar que la UPS de respaldo quedo fuera del sistema ya que se debe evaluar con IOT la mejor forma de conectar el equipo. Por otro lado solo quedan 2 baterias instaladas ya que falta tablero extra para dejarlas debidamente protegidas y funcionando."/>
+            <x14:filter val="Se instala sonda multiparametrica nueva, se conecta en tablero We control_x000a_Queda pendiente la configuración de lector RQ30._x000a_Se finaliza canalizaciones y conexionado en el punto"/>
+            <x14:filter val="Se llevó a cabo la instalación de la celda de flujo en el recinto P7, la cual incluyó el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se realizó desde la válvula de bola hasta la entrada del flowcell y, posteriormente, desde la salida del flowcell hacia el encaminado del pozo._x000a__x000a_Adicionalmente, fue necesario ejecutar trabajos de obra civil para garantizar una correcta instalación y asegurar la fijación de los elementos en sitio._x000a__x000a_Actualmente, la solución se encuentra pendiente de validación y puesta en marcha, lo cual permitirá verificar el funcionamiento integral del sistema antes de su operación continua."/>
+            <x14:filter val="Se realiza adicional de linea 1 de incorporar TC, se canaliza  linea 2 sensor de ph, el dia siguiente se terminaran los detalles, se realizan pruebas de lecturas modbus debido al problema modbus de los vdf de la PER, se trata de leer a través de reles pero sin resultado ya quebla programación es tipo escalonada. Se recomienda utilizar catrige independiente para cada vdf."/>
+            <x14:filter val="Se realiza canalización de microtubo para la llegada desde válvula hacia flowcell de sonda multiparamétrica"/>
+            <x14:filter val="Se realiza instalación de case y canalización de manguera para sonda multiparamétrica en recinto PBM4._x000a__x000a_También se realiza visita en pozos PMO en modo de levantamiento en compañía de personal de CyD, para el futuro traslado de equipos de monitoreo."/>
+            <x14:filter val="Se realiza montaje de cilindro para almacenar la sonda multiparamétrica. Además se realiza la  canalización de microtubo azul que pasa por flowcell. _x000a_"/>
+            <x14:filter val="Se realiza montaje de cilindro para almacenar sonda multiparamétrica. Además se realiza la  canalización de microtubo azul que pasa por flowcell."/>
+            <x14:filter val="Se realizan adicionales de cableado para rescatar señales modbus desde tablero de señal de humedad a tablero we, señal  se rescata desde una placa, quedaron al pendiente una vez energizado configurar la salida modbus de la placa para entregarnos el registro a leer._x000a_Se canaliza desde tablero de  bacnet modbus a tablero we señal de salida de temperatura._x000a_Se instala equipo Adam, se canaliza a tablero we cable mosbus y alimentación._x000a_Se instalan borneras para conectar señales de instrumentación y luego a Adam, queda pendiente alimentación de señales que se verá de pasada el dia siguiente. _x000a_En tablero we, se instala switch, se realizan cables de red para comunicarse entre sí con plc, se realiza bus de campo con resistencia final para lecturas modbus._x000a_"/>
+            <x14:filter val="Se realizan adicionales de cableado para rescatar señales modbus desde tablero de señal de humedad a tablero we, señal se rescata desde una placa, quedaron al pendiente una vez energizado configurar la salida modbus de la placa_x000a_para entregarnos el registro a leer._x000a_Se canaliza desde tablero de bacnet modbus a tablero we señal de salida de temperatura._x000a_Se instala equipo Adam, se canaliza a tablero we cable mosbus y alimentación._x000a_Se instalan borneras para conectar señales de instrumentación y luego a Adam._x000a_En tablero we, se instala switch y nanobox, se realizan cables de red para comunicarse entre sí con plc, se realiza bus de campo con resistencia final para lecturas modbus._x000a_Se finaliza zona 2.1 que estaba pendiente alimentación de instrumentación para lecturas analógicas._x000a_Se deja junto con gasca jumpers y cables de fibra optica a personal de cyd, registro de entrega fotográfico._x000a__x000a_Adicional: _x000a__x000a_Queda pendiente canalización de alimentación en zona 2.1._x000a_Validación de alimentación de tablero we- control en zona 1._x000a_Instalación de antena satelital._x000a_Instalación de instrumentación PH._x000a_Precomisamiento por parte de We al 100%_x000a__x000a_"/>
+            <x14:filter val="Se realizaron las conexiones entre los tableros: WE Nodo LoRa y tablero Sutron._x000a_Asimismo, se efectuó la conexión de la batería y la antena. Además, se instaló candado._x000a__x000a_Quedan pendientes las siguientes actividades:_x000a__x0009_•_x0009_Instalación del poste de hormigón._x000a__x0009_•_x0009_Colocación de la caja de registro._x000a__x0009_•_x0009_Instalación de la barra de cobre._x000a__x0009_•_x0009_Montaje del panel fotovoltaico._x000a__x0009_•_x0009_Ejecución de la canalización desde el panel fotovoltaico hacia el tablero Nodo LoRa._x000a_"/>
+            <x14:filter val="Se realizaron las conexiones entre los tableros: WE Nodo LoRa y tablero Sutron._x000a_Asimismo, se efectuó la conexión de la batería y la antena. Recinto perimetral cuenta con candado _x000a__x000a_Quedan pendientes las siguientes actividades:_x000a__x0009_•_x0009_Instalación del poste de hormigón._x000a__x0009_•_x0009_Colocación de la caja de registro._x000a__x0009_•_x0009_Instalación de la barra de cobre._x000a__x0009_•_x0009_Montaje del panel fotovoltaico._x000a__x0009_•_x0009_Ejecución de la canalización desde el panel fotovoltaico hacia el tablero Nodo LoRa."/>
+            <x14:filter val="Se realizaron las conexiones._x000a_Asimismo, se efectuó la conexión de la batería y la antena. Recinto perimetral cuenta con candado._x000a__x000a_Quedan pendientes las siguientes actividades:_x000a__x0009_•_x0009_Instalación del poste de hormigón._x000a__x0009_•_x0009_Colocación de la caja de registro._x000a__x0009_•_x0009_Instalación de la barra de cobre._x000a__x0009_•_x0009_Montaje del panel fotovoltaico._x000a__x0009_•_x0009_Ejecución de la canalización desde el panel fotovoltaico hacia el tablero Nodo LoRa.l"/>
+            <x14:filter val="Se realizo instalación de interruptor final de carrera tipo varilla para dar aviso de cortina abierta o cerrada._x000a_Se fabrica y se instala tope metalico para riel de cortina _x000a_Se realiza canalización y cableado desde interruptor hasta caja de derivación._x000a_Se validan datos en plataforma para su correcto funcionamiento."/>
+            <x14:filter val="Se realizó la instalación de la celda de flujo en el recinto O4B, incluyendo el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se efectuó desde la válvula de bola hasta la entrada del flowcell, y posteriormente desde la salida del flowcell hacia el encaminado del pozo._x000a__x000a_Asimismo, se conectó la sonda multiparamétrica al conector correspondiente de su cable._x000a__x000a_Para la validación, se efectuaron pruebas de lectura de la sonda mediante el software Hydrolab, que mide directamente la sonda HL4, y a través del software LinkComm, que recibe las lecturas del equipo Sutron._x000a__x000a_Tal como se observa en las imágenes, queda pendiente pruebas reales abriendo la válvula de bola, permitiendo el paso del agua a través de la sonda, verificando así su medición en los software mencionados y en la plataforma. De esta manera, queda pendiente verificar el flujo de entrada y salida"/>
+            <x14:filter val="Se realizó la instalación de la celda de flujo en el recinto P2G, incluyendo el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se efectuó desde la válvula de bola hasta la entrada del flowcell, y posteriormente desde la salida del flowcell hacia el encaminado del pozo._x000a__x000a_Asimismo, se conectó la sonda multiparamétrica al conector correspondiente de su cable._x000a__x000a_Para la validación, se efectuaron pruebas de lectura de la sonda mediante el software Hydrolab, que mide directamente la sonda HL4, y a través del software LinkComm, que recibe las lecturas del equipo Sutron._x000a__x000a_Tal como se observa en las imágenes, se realizaron pruebas reales abriendo la válvula de bola, permitiendo el paso del agua a través de la sonda, verificando así su medición en los softwares mencionados y en la plataforma. De esta manera, el punto quedó correctamente instalado y en monitoreo."/>
+            <x14:filter val="Se realizó la instalación de la celda de flujo en el recinto P3G, incluyendo el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se efectuó desde la válvula de bola hasta la entrada del flowcell, y posteriormente desde la salida del flowcell hacia el encaminado del pozo._x000a__x000a_Asimismo, se conectó la sonda multiparamétrica al conector correspondiente de su cable._x000a__x000a_Para la validación, se efectuaron pruebas de lectura de la sonda mediante el software Hydrolab, que mide directamente la sonda HL4, y a través del software LinkComm, que recibe las lecturas del equipo Sutron._x000a__x000a_Tal como se observa en las imágenes, se realizaron pruebas reales abriendo la válvula de bola, permitiendo el paso del agua a través de la sonda, verificando así su medición en los softwares mencionados y en la plataforma. De esta manera, el punto quedó correctamente instalado y en monitoreo."/>
+            <x14:filter val="Se realizó la instalación de la celda de flujo en el recinto P7, incluyendo el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se efectuó desde la válvula de bola hasta la entrada del flowcell, y posteriormente desde la salida del flowcell hacia el encamisado del pozo._x000a__x000a_Asimismo, se conectó la sonda multiparamétrica al conector correspondiente de su cable._x000a__x000a_Para la validación, se efectuaron pruebas de lectura de la sonda mediante el software Hydrolab, que mide directamente la sonda HL4, y a través del software LinkComm, que recibe las lecturas del equipo Sutron._x000a__x000a_Tal como se observa en las imágenes, se realizaron pruebas reales abriendo la válvula de bola, permitiendo el paso del agua a través de la sonda, verificando así su medición en los softwares mencionados y en la plataforma. De esta manera, el punto quedó correctamente instalado y en monitoreo."/>
+            <x14:filter val="Se realizó la instalación de la celda de flujo en el recinto PBM1, incluyendo el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se efectuó desde la válvula de bola hasta la entrada del flowcell y, posteriormente, desde la salida del flowcell hacia el encamizado del pozo._x000a__x000a_Como parte de la solución, se realizó el montaje completo con sus respectivos cables de extracción de agua, asegurando el paso del caudal a través del kase y del flowcell para su correcto funcionamiento._x000a__x000a_Actualmente, queda pendiente la conexión de la sonda multiparamétrica HL4, así como la configuración de sus parámetros para que las lecturas puedan ser transmitidas y visualizadas en la plataforma._x000a__x000a_Es importante destacar que el cable de la sonda presenta fallas, por lo que será necesario realizar su reemplazo para garantizar la correcta operación y transmisión de datos._x000a__x000a_Sonda multiparametrica HL4 no se deja instalada _x000a_"/>
+            <x14:filter val="Se realizó la instalación de la celda de flujo en el recinto PBM1, incluyendo el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se efectuó desde la válvula de bola hasta la entrada del flowcell, y posteriormente desde la salida del flowcell hacia el encamisado del pozo._x000a__x000a_Asimismo, se conectó la sonda multiparamétrica al conector correspondiente de su cable._x000a__x000a_Para la validación, se efectuaron pruebas de lectura de la sonda mediante el software Hydrolab, que mide directamente la sonda HL4, y a través del software LinkComm, que recibe las lecturas del equipo Sutron._x000a__x000a_Tal como se observa en las imágenes, se realizaron pruebas reales abriendo la válvula de bola, permitiendo el paso del agua a través de la sonda, verificando así su medición en los softwares mencionados y en la plataforma. De esta manera, el punto quedó correctamente instalado y en monitoreo._x000a_"/>
+            <x14:filter val="Se realizó la instalación de la celda de flujo en el recinto PBM2, incluyendo el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se efectuó desde la válvula de bola hasta la entrada del flowcell, y posteriormente desde la salida del flowcell hacia el encamisado del pozo._x000a__x000a_Asimismo, se conectó la sonda multiparamétrica al conector correspondiente de su cable._x000a__x000a_Para la validación, se efectuaron pruebas de lectura de la sonda mediante el software Hydrolab, que mide directamente la sonda HL4, y a través del software LinkComm, que recibe las lecturas del equipo Sutron._x000a__x000a_Tal como se observa en las imágenes, se realizaron pruebas reales abriendo la válvula de bola, permitiendo el paso del agua a través de la sonda, verificando así su medición en los softwares mencionados y en la plataforma. De esta manera, el punto quedó correctamente instalado y en monitoreo."/>
+            <x14:filter val="Se realizó la instalación de la celda de flujo en el recinto PBM3, incluyendo el montaje de la cámara flowcell y la instalación de un microtubo de ½”. La canalización se efectuó desde la válvula de bola hasta la entrada del flowcell, y posteriormente desde la salida del flowcell hacia el encamizado del pozo._x000a__x000a_Asimismo, se conectó la sonda multiparamétrica al conector correspondiente de su cable._x000a__x000a_Para la validación, se efectuaron pruebas de lectura de la sonda mediante el software Hydrolab, que mide directamente la sonda HL4, y a través del software LinkComm, que recibe las lecturas del equipo Sutron._x000a__x000a_Tal como se observa en las imágenes, se realizaron pruebas reales abriendo la válvula de bola, permitiendo el paso del agua a través de la sonda, verificando así su medición en los softwares mencionados y en la plataforma. De esta manera, el punto quedó correctamente instalado y en monitoreo."/>
+          </mc:Choice>
+          <mc:Fallback>
+            <filter val="Conexión entre panel solar tablero we conect solar además se canaliza a tablero we nodo Sutron la comunicación y alimentación"/>
+            <filter val="Instalacion completa de las estructuras de soportacion de los paneles, montaje de paneles y conexionado entre estos. _x000a__x000a_Canalizaciones en loza y bajada a nivel de suelo para ingreso de la alimentación fotovoltaica a tableros We Techs."/>
+            <filter val="Realizamos avances en instalacion de sensores de velocidad, canalización y cableado en estero."/>
+            <filter val="Se deja punto a punto finalizado en zona 1._x000a_Rotulacion de instrumentación en zona 1 ok._x000a_Canalizacion y cableado de quemador 2 ok_x000a_Rotulado de señales de quemador ok._x000a_Se compromete instalación de antena satélital."/>
+            <filter val="Se instala sonda multiparametrica nueva, se conecta en tablero We control_x000a_Queda pendiente la configuración de lector RQ30._x000a_Se finaliza canalizaciones y conexionado en el punto"/>
+            <filter val="Se realiza canalización de microtubo para la llegada desde válvula hacia flowcell de sonda multiparamétrica"/>
+            <filter val="Se realiza instalación de case y canalización de manguera para sonda multiparamétrica en recinto PBM4._x000a__x000a_También se realiza visita en pozos PMO en modo de levantamiento en compañía de personal de CyD, para el futuro traslado de equipos de monitoreo."/>
+            <filter val="Se realiza montaje de cilindro para almacenar la sonda multiparamétrica. Además se realiza la  canalización de microtubo azul que pasa por flowcell. _x000a_"/>
+            <filter val="Se realiza montaje de cilindro para almacenar sonda multiparamétrica. Además se realiza la  canalización de microtubo azul que pasa por flowcell."/>
+          </mc:Fallback>
+        </mc:AlternateContent>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R109">
       <sortCondition ref="H1:H109"/>
     </sortState>
@@ -11535,13 +11507,13 @@
       <c r="A4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4">
         <v>68</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4">
         <v>68</v>
       </c>
     </row>
@@ -11549,13 +11521,13 @@
       <c r="A5" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5">
         <v>36</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5">
         <v>41</v>
       </c>
     </row>
@@ -11563,13 +11535,13 @@
       <c r="A6" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6">
         <v>104</v>
       </c>
       <c r="E6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6">
         <v>6</v>
       </c>
     </row>
@@ -11577,7 +11549,7 @@
       <c r="E7" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7">
         <v>1</v>
       </c>
     </row>
@@ -11585,7 +11557,7 @@
       <c r="E8" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8">
         <v>1</v>
       </c>
     </row>
@@ -11593,7 +11565,7 @@
       <c r="E9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9">
         <v>33</v>
       </c>
     </row>
@@ -11601,7 +11573,7 @@
       <c r="E10" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10">
         <v>1</v>
       </c>
     </row>
@@ -11609,7 +11581,7 @@
       <c r="E11" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11">
         <v>1</v>
       </c>
     </row>
@@ -11617,7 +11589,7 @@
       <c r="E12" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12">
         <v>11</v>
       </c>
     </row>
@@ -11625,7 +11597,7 @@
       <c r="E13" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13">
         <v>11</v>
       </c>
     </row>
@@ -11633,7 +11605,7 @@
       <c r="E14" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14">
         <v>3</v>
       </c>
     </row>
@@ -11641,7 +11613,7 @@
       <c r="E15" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15">
         <v>1</v>
       </c>
     </row>
@@ -11649,7 +11621,7 @@
       <c r="E16" s="9" t="s">
         <v>365</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16">
         <v>1</v>
       </c>
     </row>
@@ -11657,7 +11629,7 @@
       <c r="E17" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17">
         <v>1</v>
       </c>
     </row>
@@ -11665,7 +11637,7 @@
       <c r="E18" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18">
         <v>12</v>
       </c>
     </row>
@@ -11673,7 +11645,7 @@
       <c r="E19" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19">
         <v>2</v>
       </c>
     </row>
@@ -11681,7 +11653,7 @@
       <c r="E20" s="9" t="s">
         <v>275</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20">
         <v>1</v>
       </c>
     </row>
@@ -11689,7 +11661,7 @@
       <c r="E21" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21">
         <v>4</v>
       </c>
     </row>
@@ -11697,7 +11669,7 @@
       <c r="E22" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22">
         <v>5</v>
       </c>
     </row>
@@ -11705,7 +11677,7 @@
       <c r="E23" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23">
         <v>36</v>
       </c>
     </row>
@@ -11713,7 +11685,7 @@
       <c r="E24" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24">
         <v>18</v>
       </c>
     </row>
@@ -11721,7 +11693,7 @@
       <c r="E25" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25">
         <v>4</v>
       </c>
     </row>
@@ -11729,7 +11701,7 @@
       <c r="E26" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26">
         <v>5</v>
       </c>
     </row>
@@ -11737,7 +11709,7 @@
       <c r="E27" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27">
         <v>9</v>
       </c>
     </row>
@@ -11745,7 +11717,7 @@
       <c r="E28" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28">
         <v>2</v>
       </c>
     </row>
@@ -11753,7 +11725,7 @@
       <c r="E29" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29">
         <v>2</v>
       </c>
     </row>
@@ -11761,7 +11733,7 @@
       <c r="E30" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30">
         <v>6</v>
       </c>
     </row>
@@ -11769,7 +11741,7 @@
       <c r="E31" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31">
         <v>4</v>
       </c>
     </row>
@@ -11777,7 +11749,7 @@
       <c r="E32" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32">
         <v>2</v>
       </c>
     </row>
@@ -11785,7 +11757,7 @@
       <c r="E33" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33">
         <v>1</v>
       </c>
     </row>
@@ -11793,7 +11765,7 @@
       <c r="E34" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34">
         <v>1</v>
       </c>
     </row>
@@ -11801,7 +11773,7 @@
       <c r="E35" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35">
         <v>4</v>
       </c>
     </row>
@@ -11809,7 +11781,7 @@
       <c r="E36" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36">
         <v>1</v>
       </c>
     </row>
@@ -11817,7 +11789,7 @@
       <c r="E37" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37">
         <v>3</v>
       </c>
     </row>
@@ -11825,7 +11797,7 @@
       <c r="E38" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38">
         <v>5</v>
       </c>
     </row>
@@ -11833,7 +11805,7 @@
       <c r="E39" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39">
         <v>5</v>
       </c>
     </row>
@@ -11841,7 +11813,7 @@
       <c r="E40" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40">
         <v>104</v>
       </c>
     </row>
@@ -11878,11 +11850,11 @@
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>398</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B14" s="3" t="s">
